--- a/experiments/05_gpt_proposed_terms/report/dev_v1_original_gpt_pipeline_mode_comparison.xlsx
+++ b/experiments/05_gpt_proposed_terms/report/dev_v1_original_gpt_pipeline_mode_comparison.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,11 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,12 +44,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
         <bgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
-        <bgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -82,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -90,19 +87,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -634,7 +625,7 @@
       <c r="I3" s="2" t="n">
         <v>90.59259259259258</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>gpt_proposed_term</t>
         </is>
@@ -645,7 +636,7 @@
       <c r="L3" s="2" t="n">
         <v>0.9906481481481482</v>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>gpt_proposed_term</t>
         </is>
@@ -656,7 +647,7 @@
       <c r="O3" s="2" t="n">
         <v>0.9757914338919925</v>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>gpt_proposed_term</t>
         </is>
@@ -707,7 +698,7 @@
       <c r="L4" s="2" t="n">
         <v>0.9784900284900286</v>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>gpt_proposed_term</t>
         </is>
@@ -718,69 +709,69 @@
       <c r="O4" s="2" t="n">
         <v>0.9483747609942639</v>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>gpt_proposed_term</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>enes</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="4" t="n">
         <v>48.03370230696395</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>48.10718733409574</v>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>gpt_proposed_term</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>gpt_proposed_term</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>73.0459087920281</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="4" t="n">
         <v>69.90481394422167</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>proper_term</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>proper_term</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>90.46242774566474</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="4" t="n">
         <v>99.16317991631799</v>
       </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>gpt_proposed_term</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="n">
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>gpt_proposed_term</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="n">
         <v>0.9091810922966711</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="L5" s="4" t="n">
         <v>0.9869595536959553</v>
       </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>gpt_proposed_term</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="n">
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>gpt_proposed_term</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="n">
         <v>0.8081395348837219</v>
       </c>
-      <c r="O5" s="5" t="n">
+      <c r="O5" s="4" t="n">
         <v>0.9727767695099818</v>
       </c>
-      <c r="P5" s="6" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>gpt_proposed_term</t>
         </is>

--- a/experiments/05_gpt_proposed_terms/report/dev_v1_original_gpt_pipeline_mode_comparison.xlsx
+++ b/experiments/05_gpt_proposed_terms/report/dev_v1_original_gpt_pipeline_mode_comparison.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +32,11 @@
     <font>
       <color rgb="00006100"/>
     </font>
+    <font>
+      <color rgb="009C6500"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +53,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -90,7 +99,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -467,7 +482,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -687,9 +702,9 @@
       <c r="I4" s="2" t="n">
         <v>72.22222222222221</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>proper_term</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>tie</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -716,62 +731,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>enes</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>48.03370230696395</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>48.10718733409574</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>gpt_proposed_term</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>tie</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>73.0459087920281</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>69.90481394422167</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>proper_term</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <v>90.46242774566474</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>99.16317991631799</v>
       </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>gpt_proposed_term</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="n">
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>gpt_proposed_term</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
         <v>0.9091810922966711</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="5" t="n">
         <v>0.9869595536959553</v>
       </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>gpt_proposed_term</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="n">
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>gpt_proposed_term</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="n">
         <v>0.8081395348837219</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="O5" s="5" t="n">
         <v>0.9727767695099818</v>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>gpt_proposed_term</t>
         </is>
